--- a/data/nzd0167/nzd0167.xlsx
+++ b/data/nzd0167/nzd0167.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M608"/>
+  <dimension ref="A1:M609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27784,6 +27784,51 @@
         <v>372.6</v>
       </c>
       <c r="M608" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>373.65</v>
+      </c>
+      <c r="C609" t="n">
+        <v>378.43</v>
+      </c>
+      <c r="D609" t="n">
+        <v>371.47</v>
+      </c>
+      <c r="E609" t="n">
+        <v>375.68</v>
+      </c>
+      <c r="F609" t="n">
+        <v>377.23</v>
+      </c>
+      <c r="G609" t="n">
+        <v>381.2</v>
+      </c>
+      <c r="H609" t="n">
+        <v>380.06</v>
+      </c>
+      <c r="I609" t="n">
+        <v>375.67</v>
+      </c>
+      <c r="J609" t="n">
+        <v>378.3</v>
+      </c>
+      <c r="K609" t="n">
+        <v>372.75</v>
+      </c>
+      <c r="L609" t="n">
+        <v>373.38</v>
+      </c>
+      <c r="M609" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -27800,7 +27845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B639"/>
+  <dimension ref="A1:B640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34193,6 +34238,16 @@
       </c>
       <c r="B639" t="n">
         <v>-0.43</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>
@@ -34361,28 +34416,28 @@
         <v>0.0446</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3087443235392459</v>
+        <v>-0.3097177130431386</v>
       </c>
       <c r="J2" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K2" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2623244225034109</v>
+        <v>0.2640722503586371</v>
       </c>
       <c r="M2" t="n">
-        <v>2.959674274478076</v>
+        <v>2.95965202294195</v>
       </c>
       <c r="N2" t="n">
-        <v>14.58374010472596</v>
+        <v>14.57376662806753</v>
       </c>
       <c r="O2" t="n">
-        <v>3.81886633763555</v>
+        <v>3.817560297895441</v>
       </c>
       <c r="P2" t="n">
-        <v>384.6902065107732</v>
+        <v>384.7002487555708</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -34443,28 +34498,28 @@
         <v>0.0502</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1172447248420142</v>
+        <v>-0.1193069447032357</v>
       </c>
       <c r="J3" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K3" t="n">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04131966066160297</v>
+        <v>0.04272456568167282</v>
       </c>
       <c r="M3" t="n">
-        <v>3.221544266460227</v>
+        <v>3.225710556937444</v>
       </c>
       <c r="N3" t="n">
-        <v>17.50349488122385</v>
+        <v>17.53808417501878</v>
       </c>
       <c r="O3" t="n">
-        <v>4.183717830019592</v>
+        <v>4.187849588394834</v>
       </c>
       <c r="P3" t="n">
-        <v>387.7192448114087</v>
+        <v>387.740460854564</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -34525,28 +34580,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1151071457700674</v>
+        <v>-0.1166875830877726</v>
       </c>
       <c r="J4" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K4" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09992820082404252</v>
+        <v>0.1022221562407767</v>
       </c>
       <c r="M4" t="n">
-        <v>1.836691139496045</v>
+        <v>1.840952370032141</v>
       </c>
       <c r="N4" t="n">
-        <v>6.530408797511989</v>
+        <v>6.556837591741771</v>
       </c>
       <c r="O4" t="n">
-        <v>2.555466453998563</v>
+        <v>2.560632264059362</v>
       </c>
       <c r="P4" t="n">
-        <v>379.2482331877846</v>
+        <v>379.2645084424675</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -34607,28 +34662,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.004222064513524121</v>
+        <v>-0.005389940452475613</v>
       </c>
       <c r="J5" t="n">
+        <v>608</v>
+      </c>
+      <c r="K5" t="n">
         <v>607</v>
       </c>
-      <c r="K5" t="n">
-        <v>606</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.000135114724543528</v>
+        <v>0.0002203733905903338</v>
       </c>
       <c r="M5" t="n">
-        <v>1.873392813231676</v>
+        <v>1.87641834550228</v>
       </c>
       <c r="N5" t="n">
-        <v>7.187090786134312</v>
+        <v>7.195463075776671</v>
       </c>
       <c r="O5" t="n">
-        <v>2.680875003825115</v>
+        <v>2.682436033864866</v>
       </c>
       <c r="P5" t="n">
-        <v>379.305187995788</v>
+        <v>379.3172313576914</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -34689,28 +34744,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0225219207221777</v>
+        <v>0.02137674763511936</v>
       </c>
       <c r="J6" t="n">
+        <v>608</v>
+      </c>
+      <c r="K6" t="n">
         <v>607</v>
       </c>
-      <c r="K6" t="n">
-        <v>606</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.002718247812372065</v>
+        <v>0.002453807986089962</v>
       </c>
       <c r="M6" t="n">
-        <v>2.383734792724133</v>
+        <v>2.385700390728367</v>
       </c>
       <c r="N6" t="n">
-        <v>10.1392175291747</v>
+        <v>10.14194814165617</v>
       </c>
       <c r="O6" t="n">
-        <v>3.184213800795213</v>
+        <v>3.184642545350447</v>
       </c>
       <c r="P6" t="n">
-        <v>380.0794696906899</v>
+        <v>380.0912789364065</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -34771,28 +34826,28 @@
         <v>0.083</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06385245123874589</v>
+        <v>0.06194017294973927</v>
       </c>
       <c r="J7" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K7" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02168295061785064</v>
+        <v>0.02039542732421873</v>
       </c>
       <c r="M7" t="n">
-        <v>2.415143491592896</v>
+        <v>2.421429471864825</v>
       </c>
       <c r="N7" t="n">
-        <v>10.00830801749369</v>
+        <v>10.04592964794601</v>
       </c>
       <c r="O7" t="n">
-        <v>3.163591000349713</v>
+        <v>3.169531455585512</v>
       </c>
       <c r="P7" t="n">
-        <v>385.2680855187927</v>
+        <v>385.2878140720825</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -34853,28 +34908,28 @@
         <v>0.1004</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02099033565201563</v>
+        <v>0.02009858143248176</v>
       </c>
       <c r="J8" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K8" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002842867052120557</v>
+        <v>0.002612994882224551</v>
       </c>
       <c r="M8" t="n">
-        <v>2.148090367775902</v>
+        <v>2.149081006723194</v>
       </c>
       <c r="N8" t="n">
-        <v>8.407949410133352</v>
+        <v>8.405881599544422</v>
       </c>
       <c r="O8" t="n">
-        <v>2.899646428469056</v>
+        <v>2.899289844003945</v>
       </c>
       <c r="P8" t="n">
-        <v>382.1851730742873</v>
+        <v>382.1943731058636</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -34935,28 +34990,28 @@
         <v>0.1127</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.03370142576074735</v>
+        <v>-0.03454216786875164</v>
       </c>
       <c r="J9" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K9" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L9" t="n">
-        <v>0.006299861434656218</v>
+        <v>0.006633145916690619</v>
       </c>
       <c r="M9" t="n">
-        <v>2.450649410470489</v>
+        <v>2.451673839032244</v>
       </c>
       <c r="N9" t="n">
-        <v>9.746870031391737</v>
+        <v>9.74129297072666</v>
       </c>
       <c r="O9" t="n">
-        <v>3.121997762874237</v>
+        <v>3.121104447263285</v>
       </c>
       <c r="P9" t="n">
-        <v>379.0821770152214</v>
+        <v>379.0908507660955</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -35017,28 +35072,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09170818225456422</v>
+        <v>-0.09204439089418887</v>
       </c>
       <c r="J10" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K10" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03073065098597305</v>
+        <v>0.03105644795789353</v>
       </c>
       <c r="M10" t="n">
-        <v>3.060385948142368</v>
+        <v>3.057053194776414</v>
       </c>
       <c r="N10" t="n">
-        <v>14.4322207497668</v>
+        <v>14.41015530339824</v>
       </c>
       <c r="O10" t="n">
-        <v>3.798976276546986</v>
+        <v>3.796071035083279</v>
       </c>
       <c r="P10" t="n">
-        <v>381.7222894756787</v>
+        <v>381.7257580660515</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -35099,28 +35154,28 @@
         <v>0.0667</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.192187997664977</v>
+        <v>-0.1930160619493653</v>
       </c>
       <c r="J11" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K11" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L11" t="n">
-        <v>0.129537863515906</v>
+        <v>0.1308430841829252</v>
       </c>
       <c r="M11" t="n">
-        <v>2.897204880911885</v>
+        <v>2.896002452164927</v>
       </c>
       <c r="N11" t="n">
-        <v>13.50361204270517</v>
+        <v>13.49154322934244</v>
       </c>
       <c r="O11" t="n">
-        <v>3.674726118053585</v>
+        <v>3.673083613170607</v>
       </c>
       <c r="P11" t="n">
-        <v>380.2869767621554</v>
+        <v>380.2955197187197</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -35181,28 +35236,28 @@
         <v>0.0464</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2909533567113387</v>
+        <v>-0.2920307921229643</v>
       </c>
       <c r="J12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2184992038748793</v>
+        <v>0.2202164785451061</v>
       </c>
       <c r="M12" t="n">
-        <v>3.172060493838758</v>
+        <v>3.17231222896459</v>
       </c>
       <c r="N12" t="n">
-        <v>16.47291976201895</v>
+        <v>16.46299488196939</v>
       </c>
       <c r="O12" t="n">
-        <v>4.058684486630976</v>
+        <v>4.057461630375497</v>
       </c>
       <c r="P12" t="n">
-        <v>384.262526116899</v>
+        <v>384.2736417803758</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -35244,7 +35299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M608"/>
+  <dimension ref="A1:M609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75935,6 +75990,73 @@
         </is>
       </c>
     </row>
+    <row r="609">
+      <c r="A609" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>-36.770204151334895,174.77264824094252</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>-36.76514926110595,174.767769718116</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>-36.76582745084485,174.76808496363626</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>-36.76644834424047,174.76853193934812</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>-36.767069539038815,174.7689733380881</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>-36.76764957578055,174.76945276739292</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>-36.768175612658915,174.77002847160037</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>-36.768726245223625,174.77060101520823</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>-36.769202478475876,174.7712427508377</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>-36.769638371413805,174.7719502350619</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>-36.77015337124793,174.7725928652622</t>
+        </is>
+      </c>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0167/nzd0167.xlsx
+++ b/data/nzd0167/nzd0167.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M609"/>
+  <dimension ref="A1:M612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27829,6 +27829,141 @@
         <v>373.38</v>
       </c>
       <c r="M609" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>373.61</v>
+      </c>
+      <c r="C610" t="n">
+        <v>378.55</v>
+      </c>
+      <c r="D610" t="n">
+        <v>371.24</v>
+      </c>
+      <c r="E610" t="n">
+        <v>376.08</v>
+      </c>
+      <c r="F610" t="n">
+        <v>376.54</v>
+      </c>
+      <c r="G610" t="n">
+        <v>381.1</v>
+      </c>
+      <c r="H610" t="n">
+        <v>379.52</v>
+      </c>
+      <c r="I610" t="n">
+        <v>374.79</v>
+      </c>
+      <c r="J610" t="n">
+        <v>377.44</v>
+      </c>
+      <c r="K610" t="n">
+        <v>371.66</v>
+      </c>
+      <c r="L610" t="n">
+        <v>373.05</v>
+      </c>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:12:01+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>372.1</v>
+      </c>
+      <c r="C611" t="n">
+        <v>378.47</v>
+      </c>
+      <c r="D611" t="n">
+        <v>370.58</v>
+      </c>
+      <c r="E611" t="n">
+        <v>375.08</v>
+      </c>
+      <c r="F611" t="n">
+        <v>376.35</v>
+      </c>
+      <c r="G611" t="n">
+        <v>380.96</v>
+      </c>
+      <c r="H611" t="n">
+        <v>379.42</v>
+      </c>
+      <c r="I611" t="n">
+        <v>374.6</v>
+      </c>
+      <c r="J611" t="n">
+        <v>377.34</v>
+      </c>
+      <c r="K611" t="n">
+        <v>370.84</v>
+      </c>
+      <c r="L611" t="n">
+        <v>371.88</v>
+      </c>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>372.97</v>
+      </c>
+      <c r="C612" t="n">
+        <v>378.78</v>
+      </c>
+      <c r="D612" t="n">
+        <v>370.76</v>
+      </c>
+      <c r="E612" t="n">
+        <v>375.28</v>
+      </c>
+      <c r="F612" t="n">
+        <v>376.81</v>
+      </c>
+      <c r="G612" t="n">
+        <v>381.31</v>
+      </c>
+      <c r="H612" t="n">
+        <v>379.37</v>
+      </c>
+      <c r="I612" t="n">
+        <v>374.71</v>
+      </c>
+      <c r="J612" t="n">
+        <v>377.3</v>
+      </c>
+      <c r="K612" t="n">
+        <v>371.36</v>
+      </c>
+      <c r="L612" t="n">
+        <v>372.59</v>
+      </c>
+      <c r="M612" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -27845,7 +27980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B640"/>
+  <dimension ref="A1:B643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34248,6 +34383,36 @@
       </c>
       <c r="B640" t="n">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>0.57</v>
       </c>
     </row>
   </sheetData>
@@ -34416,28 +34581,28 @@
         <v>0.0446</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3097177130431386</v>
+        <v>-0.3133182194389234</v>
       </c>
       <c r="J2" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K2" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2640722503586371</v>
+        <v>0.269861737434018</v>
       </c>
       <c r="M2" t="n">
-        <v>2.95965202294195</v>
+        <v>2.963032761201853</v>
       </c>
       <c r="N2" t="n">
-        <v>14.57376662806753</v>
+        <v>14.56827185127613</v>
       </c>
       <c r="O2" t="n">
-        <v>3.817560297895441</v>
+        <v>3.816840558796782</v>
       </c>
       <c r="P2" t="n">
-        <v>384.7002487555708</v>
+        <v>384.7375001517109</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -34498,28 +34663,28 @@
         <v>0.0502</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1193069447032357</v>
+        <v>-0.1252229444551483</v>
       </c>
       <c r="J3" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K3" t="n">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04272456568167282</v>
+        <v>0.04690643156424834</v>
       </c>
       <c r="M3" t="n">
-        <v>3.225710556937444</v>
+        <v>3.237105058734254</v>
       </c>
       <c r="N3" t="n">
-        <v>17.53808417501878</v>
+        <v>17.62666543680592</v>
       </c>
       <c r="O3" t="n">
-        <v>4.187849588394834</v>
+        <v>4.198412251888316</v>
       </c>
       <c r="P3" t="n">
-        <v>387.740460854564</v>
+        <v>387.8014968515407</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -34580,28 +34745,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1166875830877726</v>
+        <v>-0.1219510537945058</v>
       </c>
       <c r="J4" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K4" t="n">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1022221562407767</v>
+        <v>0.1096247516881544</v>
       </c>
       <c r="M4" t="n">
-        <v>1.840952370032141</v>
+        <v>1.856479136947484</v>
       </c>
       <c r="N4" t="n">
-        <v>6.556837591741771</v>
+        <v>6.663113390037416</v>
       </c>
       <c r="O4" t="n">
-        <v>2.560632264059362</v>
+        <v>2.581300716700287</v>
       </c>
       <c r="P4" t="n">
-        <v>379.2645084424675</v>
+        <v>379.3188662765265</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -34662,28 +34827,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.005389940452475613</v>
+        <v>-0.009037706300823064</v>
       </c>
       <c r="J5" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K5" t="n">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002203733905903338</v>
+        <v>0.0006204015787542039</v>
       </c>
       <c r="M5" t="n">
-        <v>1.87641834550228</v>
+        <v>1.886487942364495</v>
       </c>
       <c r="N5" t="n">
-        <v>7.195463075776671</v>
+        <v>7.227016104463917</v>
       </c>
       <c r="O5" t="n">
-        <v>2.682436033864866</v>
+        <v>2.688311013343493</v>
       </c>
       <c r="P5" t="n">
-        <v>379.3172313576914</v>
+        <v>379.3549559002003</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -34744,28 +34909,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02137674763511936</v>
+        <v>0.0173383837096092</v>
       </c>
       <c r="J6" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K6" t="n">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002453807986089962</v>
+        <v>0.001620469330660179</v>
       </c>
       <c r="M6" t="n">
-        <v>2.385700390728367</v>
+        <v>2.394626631634207</v>
       </c>
       <c r="N6" t="n">
-        <v>10.14194814165617</v>
+        <v>10.17318780102253</v>
       </c>
       <c r="O6" t="n">
-        <v>3.184642545350447</v>
+        <v>3.189543509818063</v>
       </c>
       <c r="P6" t="n">
-        <v>380.0912789364065</v>
+        <v>380.1330393146597</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -34826,28 +34991,28 @@
         <v>0.083</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06194017294973927</v>
+        <v>0.05621640792831446</v>
       </c>
       <c r="J7" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K7" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02039542732421873</v>
+        <v>0.01677651531246893</v>
       </c>
       <c r="M7" t="n">
-        <v>2.421429471864825</v>
+        <v>2.440439238994069</v>
       </c>
       <c r="N7" t="n">
-        <v>10.04592964794601</v>
+        <v>10.15896843863879</v>
       </c>
       <c r="O7" t="n">
-        <v>3.169531455585512</v>
+        <v>3.187313671203195</v>
       </c>
       <c r="P7" t="n">
-        <v>385.2878140720825</v>
+        <v>385.3470295460801</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -34908,28 +35073,28 @@
         <v>0.1004</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02009858143248176</v>
+        <v>0.01685174240868051</v>
       </c>
       <c r="J8" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K8" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002612994882224551</v>
+        <v>0.001847186183503324</v>
       </c>
       <c r="M8" t="n">
-        <v>2.149081006723194</v>
+        <v>2.155389174137987</v>
       </c>
       <c r="N8" t="n">
-        <v>8.405881599544422</v>
+        <v>8.416837244201838</v>
       </c>
       <c r="O8" t="n">
-        <v>2.899289844003945</v>
+        <v>2.901178595709309</v>
       </c>
       <c r="P8" t="n">
-        <v>382.1943731058636</v>
+        <v>382.2279643523581</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -34990,28 +35155,28 @@
         <v>0.1127</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.03454216786875164</v>
+        <v>-0.03797990724231498</v>
       </c>
       <c r="J9" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K9" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="L9" t="n">
-        <v>0.006633145916690619</v>
+        <v>0.008047792859051106</v>
       </c>
       <c r="M9" t="n">
-        <v>2.451673839032244</v>
+        <v>2.46054062229122</v>
       </c>
       <c r="N9" t="n">
-        <v>9.74129297072666</v>
+        <v>9.752022607230879</v>
       </c>
       <c r="O9" t="n">
-        <v>3.121104447263285</v>
+        <v>3.122822858765908</v>
       </c>
       <c r="P9" t="n">
-        <v>379.0908507660955</v>
+        <v>379.1264166971813</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -35072,28 +35237,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09204439089418887</v>
+        <v>-0.09396236652106388</v>
       </c>
       <c r="J10" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K10" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03105644795789353</v>
+        <v>0.03262807055986749</v>
       </c>
       <c r="M10" t="n">
-        <v>3.057053194776414</v>
+        <v>3.05178469038212</v>
       </c>
       <c r="N10" t="n">
-        <v>14.41015530339824</v>
+        <v>14.35763546074266</v>
       </c>
       <c r="O10" t="n">
-        <v>3.796071035083279</v>
+        <v>3.789147062432739</v>
       </c>
       <c r="P10" t="n">
-        <v>381.7257580660515</v>
+        <v>381.7456012634587</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -35154,28 +35319,28 @@
         <v>0.0667</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1930160619493653</v>
+        <v>-0.1968919245711319</v>
       </c>
       <c r="J11" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K11" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1308430841829252</v>
+        <v>0.1360707791752298</v>
       </c>
       <c r="M11" t="n">
-        <v>2.896002452164927</v>
+        <v>2.89825663283149</v>
       </c>
       <c r="N11" t="n">
-        <v>13.49154322934244</v>
+        <v>13.5002571679419</v>
       </c>
       <c r="O11" t="n">
-        <v>3.673083613170607</v>
+        <v>3.674269610132319</v>
       </c>
       <c r="P11" t="n">
-        <v>380.2955197187197</v>
+        <v>380.3356189193283</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -35236,28 +35401,28 @@
         <v>0.0464</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2920307921229643</v>
+        <v>-0.2960552434211094</v>
       </c>
       <c r="J12" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K12" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2202164785451061</v>
+        <v>0.2260117178624578</v>
       </c>
       <c r="M12" t="n">
-        <v>3.17231222896459</v>
+        <v>3.176984430782472</v>
       </c>
       <c r="N12" t="n">
-        <v>16.46299488196939</v>
+        <v>16.46348928656326</v>
       </c>
       <c r="O12" t="n">
-        <v>4.057461630375497</v>
+        <v>4.05752255527474</v>
       </c>
       <c r="P12" t="n">
-        <v>384.2736417803758</v>
+        <v>384.3152786469835</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -35299,7 +35464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M609"/>
+  <dimension ref="A1:M612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76057,6 +76222,207 @@
         </is>
       </c>
     </row>
+    <row r="610">
+      <c r="A610" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>-36.77020435567305,174.77264787180843</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>-36.7651487727641,174.76777091740982</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>-36.76582838606997,174.76808266448987</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>-36.76644662965476,174.7685358806175</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>-36.767072672172205,174.76896666188037</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>-36.767650118207,174.76945187286432</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>-36.76817894005842,174.77002405757287</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>-36.7687318324523,174.7705940194915</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>-36.769208545519554,174.7712367563034</t>
+        </is>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>-36.76964601690218,174.77194256879105</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>-36.77015547892946,174.77259025730382</t>
+        </is>
+      </c>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:12:01+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>-36.77021206943788,174.77263393699565</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>-36.76514909832534,174.7677701178806</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>-36.76583106975923,174.76807606693905</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>-36.766450916118785,174.76852602744378</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>-36.76707353491903,174.76896482350426</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>-36.76765087760403,174.76945062052425</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>-36.76817955624349,174.77002324016033</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>-36.76873303878572,174.77059250905253</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>-36.769209250989725,174.77123605926445</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>-36.76965176855369,174.77193680150373</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>-36.77016295161813,174.77258101090473</t>
+        </is>
+      </c>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>-36.77020762508351,174.77264196566296</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>-36.76514783677557,174.76777321605636</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>-36.76583033784401,174.76807786627114</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>-36.766450058826045,174.7685279980786</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>-36.76707144616354,174.76896927430954</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>-36.76764897911144,174.76945375137436</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>-36.76817986433603,174.77002283145404</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>-36.768732340382165,174.77059338351722</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>-36.7692095331778,174.7712357804489</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>-36.769648121164956,174.77194045880796</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>-36.77015841690971,174.77258662196763</t>
+        </is>
+      </c>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0167/nzd0167.xlsx
+++ b/data/nzd0167/nzd0167.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M612"/>
+  <dimension ref="A1:M613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27964,6 +27964,51 @@
         <v>372.59</v>
       </c>
       <c r="M612" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>373.02</v>
+      </c>
+      <c r="C613" t="n">
+        <v>378.71</v>
+      </c>
+      <c r="D613" t="n">
+        <v>369.75</v>
+      </c>
+      <c r="E613" t="n">
+        <v>373.63</v>
+      </c>
+      <c r="F613" t="n">
+        <v>376.23</v>
+      </c>
+      <c r="G613" t="n">
+        <v>381.06</v>
+      </c>
+      <c r="H613" t="n">
+        <v>377.54</v>
+      </c>
+      <c r="I613" t="n">
+        <v>374.09</v>
+      </c>
+      <c r="J613" t="n">
+        <v>376.18</v>
+      </c>
+      <c r="K613" t="n">
+        <v>370.15</v>
+      </c>
+      <c r="L613" t="n">
+        <v>372.26</v>
+      </c>
+      <c r="M613" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -27980,7 +28025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B643"/>
+  <dimension ref="A1:B644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34413,6 +34458,16 @@
       </c>
       <c r="B643" t="n">
         <v>0.57</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>-0.21</v>
       </c>
     </row>
   </sheetData>
@@ -34581,34 +34636,30 @@
         <v>0.0446</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3133182194389234</v>
+        <v>-0.3144520895260004</v>
       </c>
       <c r="J2" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K2" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L2" t="n">
-        <v>0.269861737434018</v>
+        <v>0.2717586508652445</v>
       </c>
       <c r="M2" t="n">
-        <v>2.963032761201853</v>
+        <v>2.963842367418625</v>
       </c>
       <c r="N2" t="n">
-        <v>14.56827185127613</v>
+        <v>14.56356443749037</v>
       </c>
       <c r="O2" t="n">
-        <v>3.816840558796782</v>
+        <v>3.816223845307082</v>
       </c>
       <c r="P2" t="n">
-        <v>384.7375001517109</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>384.7492866481495</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (174.769199980657 -36.77211287719463, 174.77769273291509 -36.76741151283733)</t>
@@ -34663,34 +34714,30 @@
         <v>0.0502</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1252229444551483</v>
+        <v>-0.1271321241819441</v>
       </c>
       <c r="J3" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K3" t="n">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04690643156424834</v>
+        <v>0.04830431818388103</v>
       </c>
       <c r="M3" t="n">
-        <v>3.237105058734254</v>
+        <v>3.24059351675406</v>
       </c>
       <c r="N3" t="n">
-        <v>17.62666543680592</v>
+        <v>17.65237548639939</v>
       </c>
       <c r="O3" t="n">
-        <v>4.198412251888316</v>
+        <v>4.201473013884463</v>
       </c>
       <c r="P3" t="n">
-        <v>387.8014968515407</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>387.8212896282389</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (174.76398756749137 -36.76668922942245, 174.77318688696036 -36.76294325358032)</t>
@@ -34745,34 +34792,30 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1219510537945058</v>
+        <v>-0.1240486714941343</v>
       </c>
       <c r="J4" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K4" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1096247516881544</v>
+        <v>0.1123816061588916</v>
       </c>
       <c r="M4" t="n">
-        <v>1.856479136947484</v>
+        <v>1.863510731743671</v>
       </c>
       <c r="N4" t="n">
-        <v>6.663113390037416</v>
+        <v>6.71803603439492</v>
       </c>
       <c r="O4" t="n">
-        <v>2.581300716700287</v>
+        <v>2.591917443591698</v>
       </c>
       <c r="P4" t="n">
-        <v>379.3188662765265</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>379.3406328169501</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (174.7643715676815 -36.767337864563736, 174.77357285837667 -36.76359494748067)</t>
@@ -34827,34 +34870,30 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.009037706300823064</v>
+        <v>-0.01085333825627416</v>
       </c>
       <c r="J5" t="n">
+        <v>612</v>
+      </c>
+      <c r="K5" t="n">
         <v>611</v>
       </c>
-      <c r="K5" t="n">
-        <v>610</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.0006204015787542039</v>
+        <v>0.0008917129444756533</v>
       </c>
       <c r="M5" t="n">
-        <v>1.886487942364495</v>
+        <v>1.892979810910939</v>
       </c>
       <c r="N5" t="n">
-        <v>7.227016104463917</v>
+        <v>7.264251408222438</v>
       </c>
       <c r="O5" t="n">
-        <v>2.688311013343493</v>
+        <v>2.6952275243887</v>
       </c>
       <c r="P5" t="n">
-        <v>379.3549559002003</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>379.3738212503912</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>LINESTRING (174.76483021995918 -36.768058627314986, 174.77389944532365 -36.76411310780237)</t>
@@ -34909,34 +34948,30 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0173383837096092</v>
+        <v>0.01589580295221569</v>
       </c>
       <c r="J6" t="n">
+        <v>612</v>
+      </c>
+      <c r="K6" t="n">
         <v>611</v>
       </c>
-      <c r="K6" t="n">
-        <v>610</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.001620469330660179</v>
+        <v>0.001363267552246472</v>
       </c>
       <c r="M6" t="n">
-        <v>2.394626631634207</v>
+        <v>2.398024186218108</v>
       </c>
       <c r="N6" t="n">
-        <v>10.17318780102253</v>
+        <v>10.18751071893361</v>
       </c>
       <c r="O6" t="n">
-        <v>3.189543509818063</v>
+        <v>3.191788012843837</v>
       </c>
       <c r="P6" t="n">
-        <v>380.1330393146597</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>380.1480284709616</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>LINESTRING (174.7653233049881 -36.76878240086502, 174.77422874761376 -36.764602991021555)</t>
@@ -34991,34 +35026,30 @@
         <v>0.083</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05621640792831446</v>
+        <v>0.05430735110426705</v>
       </c>
       <c r="J7" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K7" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01677651531246893</v>
+        <v>0.01564886243534513</v>
       </c>
       <c r="M7" t="n">
-        <v>2.440439238994069</v>
+        <v>2.446854580303234</v>
       </c>
       <c r="N7" t="n">
-        <v>10.15896843863879</v>
+        <v>10.19650344676855</v>
       </c>
       <c r="O7" t="n">
-        <v>3.187313671203195</v>
+        <v>3.19319643097141</v>
       </c>
       <c r="P7" t="n">
-        <v>385.3470295460801</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>385.3668740518255</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>LINESTRING (174.76604273191396 -36.769717258636454, 174.77427457160357 -36.76472551254547)</t>
@@ -35073,34 +35104,30 @@
         <v>0.1004</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01685174240868051</v>
+        <v>0.01515278526806031</v>
       </c>
       <c r="J8" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K8" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001847186183503324</v>
+        <v>0.001491950077911808</v>
       </c>
       <c r="M8" t="n">
-        <v>2.155389174137987</v>
+        <v>2.160803917248491</v>
       </c>
       <c r="N8" t="n">
-        <v>8.416837244201838</v>
+        <v>8.445959061792289</v>
       </c>
       <c r="O8" t="n">
-        <v>2.901178595709309</v>
+        <v>2.906193225130134</v>
       </c>
       <c r="P8" t="n">
-        <v>382.2279643523581</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>382.2456248872954</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>LINESTRING (174.76692171904807 -36.77051744728119, 174.77444268691443 -36.764847849442404)</t>
@@ -35155,34 +35182,30 @@
         <v>0.1127</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.03797990724231498</v>
+        <v>-0.03931344790278426</v>
       </c>
       <c r="J9" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K9" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008047792859051106</v>
+        <v>0.008626313474385361</v>
       </c>
       <c r="M9" t="n">
-        <v>2.46054062229122</v>
+        <v>2.464581238527765</v>
       </c>
       <c r="N9" t="n">
-        <v>9.752022607230879</v>
+        <v>9.762502891386941</v>
       </c>
       <c r="O9" t="n">
-        <v>3.122822858765908</v>
+        <v>3.124500422689512</v>
       </c>
       <c r="P9" t="n">
-        <v>379.1264166971813</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>379.1402787545937</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>LINESTRING (174.76761446727448 -36.771111385038985, 174.77492858097295 -36.76526974312039)</t>
@@ -35237,34 +35260,30 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09396236652106388</v>
+        <v>-0.09498056900315358</v>
       </c>
       <c r="J10" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K10" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03262807055986749</v>
+        <v>0.03339982030035682</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05178469038212</v>
+        <v>3.051953334041456</v>
       </c>
       <c r="N10" t="n">
-        <v>14.35763546074266</v>
+        <v>14.34957474167089</v>
       </c>
       <c r="O10" t="n">
-        <v>3.789147062432739</v>
+        <v>3.78808325432149</v>
       </c>
       <c r="P10" t="n">
-        <v>381.7456012634587</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>381.7561854036222</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>LINESTRING (174.7686057622454 -36.77187124492203, 174.77501773666302 -36.7653815860528)</t>
@@ -35319,34 +35338,30 @@
         <v>0.0667</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1968919245711319</v>
+        <v>-0.1985366848285036</v>
       </c>
       <c r="J11" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K11" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1360707791752298</v>
+        <v>0.1381237934802581</v>
       </c>
       <c r="M11" t="n">
-        <v>2.89825663283149</v>
+        <v>2.900434385437936</v>
       </c>
       <c r="N11" t="n">
-        <v>13.5002571679419</v>
+        <v>13.51838095282822</v>
       </c>
       <c r="O11" t="n">
-        <v>3.674269610132319</v>
+        <v>3.676735094187263</v>
       </c>
       <c r="P11" t="n">
-        <v>380.3356189193283</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>380.352716081637</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>LINESTRING (174.76932849325414 -36.77225289102588, 174.7757983679295 -36.765800421626416)</t>
@@ -35401,34 +35416,30 @@
         <v>0.0464</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2960552434211094</v>
+        <v>-0.2974526852507979</v>
       </c>
       <c r="J12" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K12" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2260117178624578</v>
+        <v>0.2280030638078026</v>
       </c>
       <c r="M12" t="n">
-        <v>3.176984430782472</v>
+        <v>3.17876740266037</v>
       </c>
       <c r="N12" t="n">
-        <v>16.46348928656326</v>
+        <v>16.46559530204332</v>
       </c>
       <c r="O12" t="n">
-        <v>4.05752255527474</v>
+        <v>4.057782066849244</v>
       </c>
       <c r="P12" t="n">
-        <v>384.3152786469835</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>384.3298049523658</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>LINESTRING (174.76964198753947 -36.77253808251128, 174.77691295410548 -36.76666175938218)</t>
@@ -35464,7 +35475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M612"/>
+  <dimension ref="A1:M613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76423,6 +76434,73 @@
         </is>
       </c>
     </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>-36.770207369660824,174.77264242708063</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>-36.76514812164166,174.76777251646828</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>-36.76583444470129,174.7680677700184</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>-36.76645713149021,174.7685117403399</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>-36.767074079811735,174.76896366242457</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>-36.767650335177585,174.76945151505288</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>-36.76819114052194,174.77000787280213</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>-36.76873627683845,174.77058845471612</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>-36.769217434443505,174.77122797361193</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>-36.76965660835781,174.77193194854175</t>
+        </is>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>-36.77016052459111,174.7725840140089</t>
+        </is>
+      </c>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0167/nzd0167.xlsx
+++ b/data/nzd0167/nzd0167.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M613"/>
+  <dimension ref="A1:M616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28011,6 +28011,141 @@
       <c r="M613" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>372.55</v>
+      </c>
+      <c r="C614" t="n">
+        <v>379.38</v>
+      </c>
+      <c r="D614" t="n">
+        <v>370.54</v>
+      </c>
+      <c r="E614" t="n">
+        <v>374.46</v>
+      </c>
+      <c r="F614" t="n">
+        <v>377.45</v>
+      </c>
+      <c r="G614" t="n">
+        <v>382.51</v>
+      </c>
+      <c r="H614" t="n">
+        <v>378.72</v>
+      </c>
+      <c r="I614" t="n">
+        <v>375.01</v>
+      </c>
+      <c r="J614" t="n">
+        <v>376.27</v>
+      </c>
+      <c r="K614" t="n">
+        <v>369.6</v>
+      </c>
+      <c r="L614" t="n">
+        <v>371.87</v>
+      </c>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:11:49+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>371.46</v>
+      </c>
+      <c r="C615" t="n">
+        <v>379.36</v>
+      </c>
+      <c r="D615" t="n">
+        <v>370.79</v>
+      </c>
+      <c r="E615" t="n">
+        <v>374.72</v>
+      </c>
+      <c r="F615" t="n">
+        <v>378.03</v>
+      </c>
+      <c r="G615" t="n">
+        <v>383.45</v>
+      </c>
+      <c r="H615" t="n">
+        <v>379.53</v>
+      </c>
+      <c r="I615" t="n">
+        <v>375.48</v>
+      </c>
+      <c r="J615" t="n">
+        <v>376.87</v>
+      </c>
+      <c r="K615" t="n">
+        <v>369.81</v>
+      </c>
+      <c r="L615" t="n">
+        <v>371.3</v>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="n">
+        <v>374.63</v>
+      </c>
+      <c r="C616" t="n">
+        <v>380.73</v>
+      </c>
+      <c r="D616" t="n">
+        <v>371.97</v>
+      </c>
+      <c r="E616" t="n">
+        <v>376.61</v>
+      </c>
+      <c r="F616" t="n">
+        <v>379</v>
+      </c>
+      <c r="G616" t="n">
+        <v>384.44</v>
+      </c>
+      <c r="H616" t="n">
+        <v>380.16</v>
+      </c>
+      <c r="I616" t="n">
+        <v>376.03</v>
+      </c>
+      <c r="J616" t="n">
+        <v>377.57</v>
+      </c>
+      <c r="K616" t="n">
+        <v>371.6</v>
+      </c>
+      <c r="L616" t="n">
+        <v>373.7</v>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28025,7 +28160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B644"/>
+  <dimension ref="A1:B647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34468,6 +34603,36 @@
       </c>
       <c r="B644" t="n">
         <v>-0.21</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
@@ -34636,28 +34801,28 @@
         <v>0.0446</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3144520895260004</v>
+        <v>-0.3179146718935465</v>
       </c>
       <c r="J2" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="K2" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2717586508652445</v>
+        <v>0.2773954654850485</v>
       </c>
       <c r="M2" t="n">
-        <v>2.963842367418625</v>
+        <v>2.966554674914059</v>
       </c>
       <c r="N2" t="n">
-        <v>14.56356443749037</v>
+        <v>14.56059394549845</v>
       </c>
       <c r="O2" t="n">
-        <v>3.816223845307082</v>
+        <v>3.815834632881574</v>
       </c>
       <c r="P2" t="n">
-        <v>384.7492866481495</v>
+        <v>384.7853927389353</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34714,28 +34879,28 @@
         <v>0.0502</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1271321241819441</v>
+        <v>-0.1316746150424383</v>
       </c>
       <c r="J3" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="K3" t="n">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04830431818388103</v>
+        <v>0.05188402782446733</v>
       </c>
       <c r="M3" t="n">
-        <v>3.24059351675406</v>
+        <v>3.245884150989071</v>
       </c>
       <c r="N3" t="n">
-        <v>17.65237548639939</v>
+        <v>17.67113628001121</v>
       </c>
       <c r="O3" t="n">
-        <v>4.201473013884463</v>
+        <v>4.20370506577367</v>
       </c>
       <c r="P3" t="n">
-        <v>387.8212896282389</v>
+        <v>387.8685374480826</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34792,28 +34957,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1240486714941343</v>
+        <v>-0.1289122456962777</v>
       </c>
       <c r="J4" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="K4" t="n">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1123816061588916</v>
+        <v>0.1195703745673614</v>
       </c>
       <c r="M4" t="n">
-        <v>1.863510731743671</v>
+        <v>1.878636736078466</v>
       </c>
       <c r="N4" t="n">
-        <v>6.71803603439492</v>
+        <v>6.80536069924468</v>
       </c>
       <c r="O4" t="n">
-        <v>2.591917443591698</v>
+        <v>2.608708626743255</v>
       </c>
       <c r="P4" t="n">
-        <v>379.3406328169501</v>
+        <v>379.3912662710219</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34870,28 +35035,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01085333825627416</v>
+        <v>-0.01461024392539296</v>
       </c>
       <c r="J5" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="K5" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0008917129444756533</v>
+        <v>0.00161599994982442</v>
       </c>
       <c r="M5" t="n">
-        <v>1.892979810910939</v>
+        <v>1.903524093167484</v>
       </c>
       <c r="N5" t="n">
-        <v>7.264251408222438</v>
+        <v>7.303507449025355</v>
       </c>
       <c r="O5" t="n">
-        <v>2.6952275243887</v>
+        <v>2.702500221836319</v>
       </c>
       <c r="P5" t="n">
-        <v>379.3738212503912</v>
+        <v>379.4129795203311</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34948,28 +35113,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01589580295221569</v>
+        <v>0.01352859842149954</v>
       </c>
       <c r="J6" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="K6" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001363267552246472</v>
+        <v>0.000995894967309896</v>
       </c>
       <c r="M6" t="n">
-        <v>2.398024186218108</v>
+        <v>2.398296971260886</v>
       </c>
       <c r="N6" t="n">
-        <v>10.18751071893361</v>
+        <v>10.16762732636075</v>
       </c>
       <c r="O6" t="n">
-        <v>3.191788012843837</v>
+        <v>3.188671718186234</v>
       </c>
       <c r="P6" t="n">
-        <v>380.1480284709616</v>
+        <v>380.1727006905838</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35026,28 +35191,28 @@
         <v>0.083</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05430735110426705</v>
+        <v>0.05102436688975055</v>
       </c>
       <c r="J7" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="K7" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01564886243534513</v>
+        <v>0.01391501891148406</v>
       </c>
       <c r="M7" t="n">
-        <v>2.446854580303234</v>
+        <v>2.452839010489056</v>
       </c>
       <c r="N7" t="n">
-        <v>10.19650344676855</v>
+        <v>10.20334134514263</v>
       </c>
       <c r="O7" t="n">
-        <v>3.19319643097141</v>
+        <v>3.194266949574288</v>
       </c>
       <c r="P7" t="n">
-        <v>385.3668740518255</v>
+        <v>385.4011060974969</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35104,28 +35269,28 @@
         <v>0.1004</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01515278526806031</v>
+        <v>0.01202511223534133</v>
       </c>
       <c r="J8" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="K8" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001491950077911808</v>
+        <v>0.0009449501300011764</v>
       </c>
       <c r="M8" t="n">
-        <v>2.160803917248491</v>
+        <v>2.166663247557358</v>
       </c>
       <c r="N8" t="n">
-        <v>8.445959061792289</v>
+        <v>8.455035404684539</v>
       </c>
       <c r="O8" t="n">
-        <v>2.906193225130134</v>
+        <v>2.907754357693328</v>
       </c>
       <c r="P8" t="n">
-        <v>382.2456248872954</v>
+        <v>382.2782393203154</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35182,28 +35347,28 @@
         <v>0.1127</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.03931344790278426</v>
+        <v>-0.04185786973081739</v>
       </c>
       <c r="J9" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="K9" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008626313474385361</v>
+        <v>0.009842483747143249</v>
       </c>
       <c r="M9" t="n">
-        <v>2.464581238527765</v>
+        <v>2.467995339292884</v>
       </c>
       <c r="N9" t="n">
-        <v>9.762502891386941</v>
+        <v>9.747886179894834</v>
       </c>
       <c r="O9" t="n">
-        <v>3.124500422689512</v>
+        <v>3.122160498740389</v>
       </c>
       <c r="P9" t="n">
-        <v>379.1402787545937</v>
+        <v>379.1668120070429</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35260,28 +35425,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09498056900315358</v>
+        <v>-0.09727256095597719</v>
       </c>
       <c r="J10" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="K10" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03339982030035682</v>
+        <v>0.03528462437611413</v>
       </c>
       <c r="M10" t="n">
-        <v>3.051953334041456</v>
+        <v>3.048685187985816</v>
       </c>
       <c r="N10" t="n">
-        <v>14.34957474167089</v>
+        <v>14.30708064096313</v>
       </c>
       <c r="O10" t="n">
-        <v>3.78808325432149</v>
+        <v>3.782470177141272</v>
       </c>
       <c r="P10" t="n">
-        <v>381.7561854036222</v>
+        <v>381.7800844476774</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35338,28 +35503,28 @@
         <v>0.0667</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1985366848285036</v>
+        <v>-0.2032018480634867</v>
       </c>
       <c r="J11" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="K11" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1381237934802581</v>
+        <v>0.1440907354295131</v>
       </c>
       <c r="M11" t="n">
-        <v>2.900434385437936</v>
+        <v>2.905714315885156</v>
       </c>
       <c r="N11" t="n">
-        <v>13.51838095282822</v>
+        <v>13.56449405002963</v>
       </c>
       <c r="O11" t="n">
-        <v>3.676735094187263</v>
+        <v>3.683000685586364</v>
       </c>
       <c r="P11" t="n">
-        <v>380.352716081637</v>
+        <v>380.4013643488846</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35416,28 +35581,28 @@
         <v>0.0464</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2974526852507979</v>
+        <v>-0.3015283641657884</v>
       </c>
       <c r="J12" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="K12" t="n">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2280030638078026</v>
+        <v>0.2338574176781723</v>
       </c>
       <c r="M12" t="n">
-        <v>3.17876740266037</v>
+        <v>3.183432201928343</v>
       </c>
       <c r="N12" t="n">
-        <v>16.46559530204332</v>
+        <v>16.47295142657481</v>
       </c>
       <c r="O12" t="n">
-        <v>4.057782066849244</v>
+        <v>4.058688387468888</v>
       </c>
       <c r="P12" t="n">
-        <v>384.3298049523658</v>
+        <v>384.3723062766213</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35475,7 +35640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M613"/>
+  <dimension ref="A1:M616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76501,6 +76666,207 @@
         </is>
       </c>
     </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>-36.77020977063397,174.77263808975474</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>-36.76514539506613,174.76777921252517</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>-36.76583123240705,174.76807566708746</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>-36.766453573726075,174.7685199184755</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>-36.767068540068664,174.76897546673393</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>-36.767642469993426,174.76946448571638</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>-36.76818386953889,174.77001751827217</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>-36.76873043564518,174.77059576842078</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>-36.769216799520386,174.7712286009471</t>
+        </is>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>-36.76966046617256,174.7719280802383</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>-36.770163015487256,174.7725809318757</t>
+        </is>
+      </c>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:11:49+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>-36.77021533884767,174.772628030849</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>-36.76514547645646,174.7677790126429</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>-36.76583021585815,174.76807816615982</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>-36.766452459245635,174.76852248030096</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>-36.767065906419916,174.7689810786181</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>-36.76763737118367,174.769472894283</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>-36.76817887843991,174.77002413931413</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>-36.76872745155713,174.77059950476948</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>-36.769212566699515,174.77123278318132</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>-36.76965899318876,174.77192955722694</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>-36.77016665602764,174.77257642721906</t>
+        </is>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>-36.770199145049574,174.77265728472673</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>-36.765139901218824,174.76779270457865</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>-36.76582541774659,174.7680899617804</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>-36.76644435782851,174.7685411027991</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>-36.76706150186886,174.76899046400973</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>-36.76763200116,174.7694817501126</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>-36.768174996473796,174.77002928901283</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>-36.768723959539074,174.77060387709204</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>-36.76920762840833,174.77123766245398</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>-36.76964643775476,174.77194214679443</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>-36.77015132743548,174.7725953941914</t>
+        </is>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0167/nzd0167.xlsx
+++ b/data/nzd0167/nzd0167.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M616"/>
+  <dimension ref="A1:M618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28146,6 +28146,96 @@
       <c r="M616" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>374.92</v>
+      </c>
+      <c r="C617" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="D617" t="n">
+        <v>372.65</v>
+      </c>
+      <c r="E617" t="n">
+        <v>376.71</v>
+      </c>
+      <c r="F617" t="n">
+        <v>379.2</v>
+      </c>
+      <c r="G617" t="n">
+        <v>385.16</v>
+      </c>
+      <c r="H617" t="n">
+        <v>381.47</v>
+      </c>
+      <c r="I617" t="n">
+        <v>376.89</v>
+      </c>
+      <c r="J617" t="n">
+        <v>378.39</v>
+      </c>
+      <c r="K617" t="n">
+        <v>372.49</v>
+      </c>
+      <c r="L617" t="n">
+        <v>373.87</v>
+      </c>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>373.69</v>
+      </c>
+      <c r="C618" t="n">
+        <v>381.59</v>
+      </c>
+      <c r="D618" t="n">
+        <v>373.46</v>
+      </c>
+      <c r="E618" t="n">
+        <v>377.45</v>
+      </c>
+      <c r="F618" t="n">
+        <v>379.31</v>
+      </c>
+      <c r="G618" t="n">
+        <v>385.53</v>
+      </c>
+      <c r="H618" t="n">
+        <v>382.08</v>
+      </c>
+      <c r="I618" t="n">
+        <v>377.27</v>
+      </c>
+      <c r="J618" t="n">
+        <v>379.19</v>
+      </c>
+      <c r="K618" t="n">
+        <v>372.74</v>
+      </c>
+      <c r="L618" t="n">
+        <v>372.84</v>
+      </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28160,7 +28250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B647"/>
+  <dimension ref="A1:B649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34633,6 +34723,26 @@
       </c>
       <c r="B647" t="n">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>-0.7</v>
       </c>
     </row>
   </sheetData>
@@ -34801,28 +34911,28 @@
         <v>0.0446</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3179146718935465</v>
+        <v>-0.3192365450500769</v>
       </c>
       <c r="J2" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="K2" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2773954654850485</v>
+        <v>0.2803453617314638</v>
       </c>
       <c r="M2" t="n">
-        <v>2.966554674914059</v>
+        <v>2.96345961786034</v>
       </c>
       <c r="N2" t="n">
-        <v>14.56059394549845</v>
+        <v>14.52772235524572</v>
       </c>
       <c r="O2" t="n">
-        <v>3.815834632881574</v>
+        <v>3.811524938295133</v>
       </c>
       <c r="P2" t="n">
-        <v>384.7853927389353</v>
+        <v>384.7992262587003</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34879,28 +34989,28 @@
         <v>0.0502</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1316746150424383</v>
+        <v>-0.1334794735702009</v>
       </c>
       <c r="J3" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="K3" t="n">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05188402782446733</v>
+        <v>0.05353929291754156</v>
       </c>
       <c r="M3" t="n">
-        <v>3.245884150989071</v>
+        <v>3.243752350330644</v>
       </c>
       <c r="N3" t="n">
-        <v>17.67113628001121</v>
+        <v>17.6380853851031</v>
       </c>
       <c r="O3" t="n">
-        <v>4.20370506577367</v>
+        <v>4.199772063470005</v>
       </c>
       <c r="P3" t="n">
-        <v>387.8685374480826</v>
+        <v>387.8873713657946</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34957,28 +35067,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1289122456962777</v>
+        <v>-0.1308085625237575</v>
       </c>
       <c r="J4" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="K4" t="n">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1195703745673614</v>
+        <v>0.1230291970220774</v>
       </c>
       <c r="M4" t="n">
-        <v>1.878636736078466</v>
+        <v>1.882162826677199</v>
       </c>
       <c r="N4" t="n">
-        <v>6.80536069924468</v>
+        <v>6.810974987896739</v>
       </c>
       <c r="O4" t="n">
-        <v>2.608708626743255</v>
+        <v>2.609784471541039</v>
       </c>
       <c r="P4" t="n">
-        <v>379.3912662710219</v>
+        <v>379.4110694771062</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35035,28 +35145,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01461024392539296</v>
+        <v>-0.01587804279571029</v>
       </c>
       <c r="J5" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="K5" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00161599994982442</v>
+        <v>0.001918813516925577</v>
       </c>
       <c r="M5" t="n">
-        <v>1.903524093167484</v>
+        <v>1.90403876720122</v>
       </c>
       <c r="N5" t="n">
-        <v>7.303507449025355</v>
+        <v>7.292359725149717</v>
       </c>
       <c r="O5" t="n">
-        <v>2.702500221836319</v>
+        <v>2.700436950782172</v>
       </c>
       <c r="P5" t="n">
-        <v>379.4129795203311</v>
+        <v>379.4262353088766</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35113,28 +35223,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01352859842149954</v>
+        <v>0.01269588249513587</v>
       </c>
       <c r="J6" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="K6" t="n">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000995894967309896</v>
+        <v>0.000883184718806107</v>
       </c>
       <c r="M6" t="n">
-        <v>2.398296971260886</v>
+        <v>2.394736842289169</v>
       </c>
       <c r="N6" t="n">
-        <v>10.16762732636075</v>
+        <v>10.13985064089734</v>
       </c>
       <c r="O6" t="n">
-        <v>3.188671718186234</v>
+        <v>3.184313213378567</v>
       </c>
       <c r="P6" t="n">
-        <v>380.1727006905838</v>
+        <v>380.1814086461385</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35191,28 +35301,28 @@
         <v>0.083</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05102436688975055</v>
+        <v>0.05010179168518973</v>
       </c>
       <c r="J7" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="K7" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01391501891148406</v>
+        <v>0.01351229808192722</v>
       </c>
       <c r="M7" t="n">
-        <v>2.452839010489056</v>
+        <v>2.44992652246221</v>
       </c>
       <c r="N7" t="n">
-        <v>10.20334134514263</v>
+        <v>10.1767837398529</v>
       </c>
       <c r="O7" t="n">
-        <v>3.194266949574288</v>
+        <v>3.190107167455805</v>
       </c>
       <c r="P7" t="n">
-        <v>385.4011060974969</v>
+        <v>385.4107568118004</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35269,28 +35379,28 @@
         <v>0.1004</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01202511223534133</v>
+        <v>0.01148730522424489</v>
       </c>
       <c r="J8" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="K8" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0009449501300011764</v>
+        <v>0.0008684951639384986</v>
       </c>
       <c r="M8" t="n">
-        <v>2.166663247557358</v>
+        <v>2.1625070076633</v>
       </c>
       <c r="N8" t="n">
-        <v>8.455035404684539</v>
+        <v>8.43010810570123</v>
       </c>
       <c r="O8" t="n">
-        <v>2.907754357693328</v>
+        <v>2.903464844922568</v>
       </c>
       <c r="P8" t="n">
-        <v>382.2782393203154</v>
+        <v>382.2838637933912</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35347,28 +35457,28 @@
         <v>0.1127</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.04185786973081739</v>
+        <v>-0.04249439520926748</v>
       </c>
       <c r="J9" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="K9" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009842483747143249</v>
+        <v>0.01021186517909844</v>
       </c>
       <c r="M9" t="n">
-        <v>2.467995339292884</v>
+        <v>2.463876301119614</v>
       </c>
       <c r="N9" t="n">
-        <v>9.747886179894834</v>
+        <v>9.719458053791477</v>
       </c>
       <c r="O9" t="n">
-        <v>3.122160498740389</v>
+        <v>3.117604537748731</v>
       </c>
       <c r="P9" t="n">
-        <v>379.1668120070429</v>
+        <v>379.1734700287957</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35425,28 +35535,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09727256095597719</v>
+        <v>-0.0975370762008939</v>
       </c>
       <c r="J10" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="K10" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03528462437611413</v>
+        <v>0.03571997676652394</v>
       </c>
       <c r="M10" t="n">
-        <v>3.048685187985816</v>
+        <v>3.040143667008292</v>
       </c>
       <c r="N10" t="n">
-        <v>14.30708064096313</v>
+        <v>14.26175729555016</v>
       </c>
       <c r="O10" t="n">
-        <v>3.782470177141272</v>
+        <v>3.776474188386591</v>
       </c>
       <c r="P10" t="n">
-        <v>381.7800844476774</v>
+        <v>381.7828490892736</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35503,28 +35613,28 @@
         <v>0.0667</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2032018480634867</v>
+        <v>-0.2047546272314211</v>
       </c>
       <c r="J11" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="K11" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1440907354295131</v>
+        <v>0.1467297075007075</v>
       </c>
       <c r="M11" t="n">
-        <v>2.905714315885156</v>
+        <v>2.902705285508603</v>
       </c>
       <c r="N11" t="n">
-        <v>13.56449405002963</v>
+        <v>13.53871972174677</v>
       </c>
       <c r="O11" t="n">
-        <v>3.683000685586364</v>
+        <v>3.679499928216709</v>
       </c>
       <c r="P11" t="n">
-        <v>380.4013643488846</v>
+        <v>380.4176086017189</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35581,28 +35691,28 @@
         <v>0.0464</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3015283641657884</v>
+        <v>-0.3034861673000061</v>
       </c>
       <c r="J12" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="K12" t="n">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2338574176781723</v>
+        <v>0.2371877690652261</v>
       </c>
       <c r="M12" t="n">
-        <v>3.183432201928343</v>
+        <v>3.182980996764109</v>
       </c>
       <c r="N12" t="n">
-        <v>16.47295142657481</v>
+        <v>16.44919819177223</v>
       </c>
       <c r="O12" t="n">
-        <v>4.058688387468888</v>
+        <v>4.05576111128013</v>
       </c>
       <c r="P12" t="n">
-        <v>384.3723062766213</v>
+        <v>384.3927922064578</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35640,7 +35750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M616"/>
+  <dimension ref="A1:M618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76867,6 +76977,140 @@
         </is>
       </c>
     </row>
+    <row r="617">
+      <c r="A617" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>-36.77019766359767,174.77265996094837</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>-36.76513636073867,174.7678013994565</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>-36.76582265273265,174.76809675925597</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>-36.76644392918203,174.76854208811636</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>-36.76706059371392,174.7689923991419</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>-36.767628095687854,174.76948819071518</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>-36.76816692444835,174.7700399971148</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>-36.76871849929233,174.77061071381382</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>-36.76920184355267,174.77124337817264</t>
+        </is>
+      </c>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>-36.76964019510832,174.77194840641027</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>-36.77015024166008,174.772596737685</t>
+        </is>
+      </c>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>-36.77020394699672,174.7726486100766</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>-36.765136401433836,174.76780129951538</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>-36.76581935911261,174.76810485624833</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>-36.76644075719776,174.76854937946368</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>-36.76706009422868,174.76899346346457</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>-36.76762608870899,174.769491500469</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>-36.76816316571864,174.77004498332946</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>-36.768716086625055,174.77061373469056</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>-36.76919619979083,174.7712489544827</t>
+        </is>
+      </c>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>-36.76963844155589,174.77195016472913</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>-36.77015682018132,174.77258859769384</t>
+        </is>
+      </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0167/nzd0167.xlsx
+++ b/data/nzd0167/nzd0167.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M618"/>
+  <dimension ref="A1:M624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28236,6 +28236,276 @@
       <c r="M618" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>374.43</v>
+      </c>
+      <c r="C619" t="n">
+        <v>381.52</v>
+      </c>
+      <c r="D619" t="n">
+        <v>373.79</v>
+      </c>
+      <c r="E619" t="n">
+        <v>377.81</v>
+      </c>
+      <c r="F619" t="n">
+        <v>379.8</v>
+      </c>
+      <c r="G619" t="n">
+        <v>386.33</v>
+      </c>
+      <c r="H619" t="n">
+        <v>382.76</v>
+      </c>
+      <c r="I619" t="n">
+        <v>377.36</v>
+      </c>
+      <c r="J619" t="n">
+        <v>379.6</v>
+      </c>
+      <c r="K619" t="n">
+        <v>373.15</v>
+      </c>
+      <c r="L619" t="n">
+        <v>373.45</v>
+      </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>373.91</v>
+      </c>
+      <c r="C620" t="n">
+        <v>381.05</v>
+      </c>
+      <c r="D620" t="n">
+        <v>373.58</v>
+      </c>
+      <c r="E620" t="n">
+        <v>377.1</v>
+      </c>
+      <c r="F620" t="n">
+        <v>379.62</v>
+      </c>
+      <c r="G620" t="n">
+        <v>385.9</v>
+      </c>
+      <c r="H620" t="n">
+        <v>382.47</v>
+      </c>
+      <c r="I620" t="n">
+        <v>377.23</v>
+      </c>
+      <c r="J620" t="n">
+        <v>379.13</v>
+      </c>
+      <c r="K620" t="n">
+        <v>372.8</v>
+      </c>
+      <c r="L620" t="n">
+        <v>373.1</v>
+      </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>373.82</v>
+      </c>
+      <c r="C621" t="n">
+        <v>382.38</v>
+      </c>
+      <c r="D621" t="n">
+        <v>374.39</v>
+      </c>
+      <c r="E621" t="n">
+        <v>378.06</v>
+      </c>
+      <c r="F621" t="n">
+        <v>380.4</v>
+      </c>
+      <c r="G621" t="n">
+        <v>386.99</v>
+      </c>
+      <c r="H621" t="n">
+        <v>383.21</v>
+      </c>
+      <c r="I621" t="n">
+        <v>377.7</v>
+      </c>
+      <c r="J621" t="n">
+        <v>379.48</v>
+      </c>
+      <c r="K621" t="n">
+        <v>373.28</v>
+      </c>
+      <c r="L621" t="n">
+        <v>373.35</v>
+      </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>373.47</v>
+      </c>
+      <c r="C622" t="n">
+        <v>381.91</v>
+      </c>
+      <c r="D622" t="n">
+        <v>374.15</v>
+      </c>
+      <c r="E622" t="n">
+        <v>377.68</v>
+      </c>
+      <c r="F622" t="n">
+        <v>380.3</v>
+      </c>
+      <c r="G622" t="n">
+        <v>386.89</v>
+      </c>
+      <c r="H622" t="n">
+        <v>383.39</v>
+      </c>
+      <c r="I622" t="n">
+        <v>377.88</v>
+      </c>
+      <c r="J622" t="n">
+        <v>379.66</v>
+      </c>
+      <c r="K622" t="n">
+        <v>372.99</v>
+      </c>
+      <c r="L622" t="n">
+        <v>373.31</v>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>373.86</v>
+      </c>
+      <c r="C623" t="n">
+        <v>382.12</v>
+      </c>
+      <c r="D623" t="n">
+        <v>374.22</v>
+      </c>
+      <c r="E623" t="n">
+        <v>377.75</v>
+      </c>
+      <c r="F623" t="n">
+        <v>380.21</v>
+      </c>
+      <c r="G623" t="n">
+        <v>387.14</v>
+      </c>
+      <c r="H623" t="n">
+        <v>383.52</v>
+      </c>
+      <c r="I623" t="n">
+        <v>378</v>
+      </c>
+      <c r="J623" t="n">
+        <v>379.8</v>
+      </c>
+      <c r="K623" t="n">
+        <v>373.11</v>
+      </c>
+      <c r="L623" t="n">
+        <v>373.66</v>
+      </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>373.97</v>
+      </c>
+      <c r="C624" t="n">
+        <v>383.47</v>
+      </c>
+      <c r="D624" t="n">
+        <v>374.47</v>
+      </c>
+      <c r="E624" t="n">
+        <v>377.59</v>
+      </c>
+      <c r="F624" t="n">
+        <v>380.1</v>
+      </c>
+      <c r="G624" t="n">
+        <v>387.28</v>
+      </c>
+      <c r="H624" t="n">
+        <v>383.49</v>
+      </c>
+      <c r="I624" t="n">
+        <v>378.17</v>
+      </c>
+      <c r="J624" t="n">
+        <v>379.82</v>
+      </c>
+      <c r="K624" t="n">
+        <v>373.16</v>
+      </c>
+      <c r="L624" t="n">
+        <v>373.87</v>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28250,7 +28520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B649"/>
+  <dimension ref="A1:B655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34743,6 +35013,66 @@
       </c>
       <c r="B649" t="n">
         <v>-0.7</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -34911,28 +35241,28 @@
         <v>0.0446</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3192365450500769</v>
+        <v>-0.3237639875058856</v>
       </c>
       <c r="J2" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="K2" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2803453617314638</v>
+        <v>0.2897832112087508</v>
       </c>
       <c r="M2" t="n">
-        <v>2.96345961786034</v>
+        <v>2.956928438873497</v>
       </c>
       <c r="N2" t="n">
-        <v>14.52772235524572</v>
+        <v>14.44076536342874</v>
       </c>
       <c r="O2" t="n">
-        <v>3.811524938295133</v>
+        <v>3.800100704379918</v>
       </c>
       <c r="P2" t="n">
-        <v>384.7992262587003</v>
+        <v>384.8467774507401</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34989,28 +35319,28 @@
         <v>0.0502</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1334794735702009</v>
+        <v>-0.1377720915732681</v>
       </c>
       <c r="J3" t="n">
+        <v>623</v>
+      </c>
+      <c r="K3" t="n">
         <v>617</v>
       </c>
-      <c r="K3" t="n">
-        <v>611</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.05353929291754156</v>
+        <v>0.05785044861265964</v>
       </c>
       <c r="M3" t="n">
-        <v>3.243752350330644</v>
+        <v>3.232467981444384</v>
       </c>
       <c r="N3" t="n">
-        <v>17.6380853851031</v>
+        <v>17.51973338995992</v>
       </c>
       <c r="O3" t="n">
-        <v>4.199772063470005</v>
+        <v>4.185658059368912</v>
       </c>
       <c r="P3" t="n">
-        <v>387.8873713657946</v>
+        <v>387.9323231984067</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35067,28 +35397,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1308085625237575</v>
+        <v>-0.1342833581698071</v>
       </c>
       <c r="J4" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="K4" t="n">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1230291970220774</v>
+        <v>0.1307226862988865</v>
       </c>
       <c r="M4" t="n">
-        <v>1.882162826677199</v>
+        <v>1.881670527833731</v>
       </c>
       <c r="N4" t="n">
-        <v>6.810974987896739</v>
+        <v>6.776975276693554</v>
       </c>
       <c r="O4" t="n">
-        <v>2.609784471541039</v>
+        <v>2.603262429470674</v>
       </c>
       <c r="P4" t="n">
-        <v>379.4110694771062</v>
+        <v>379.4474950954695</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35145,28 +35475,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01587804279571029</v>
+        <v>-0.01843976210079783</v>
       </c>
       <c r="J5" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="K5" t="n">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001918813516925577</v>
+        <v>0.002636652058507272</v>
       </c>
       <c r="M5" t="n">
-        <v>1.90403876720122</v>
+        <v>1.899438951044583</v>
       </c>
       <c r="N5" t="n">
-        <v>7.292359725149717</v>
+        <v>7.239584984170277</v>
       </c>
       <c r="O5" t="n">
-        <v>2.700436950782172</v>
+        <v>2.690647688600326</v>
       </c>
       <c r="P5" t="n">
-        <v>379.4262353088766</v>
+        <v>379.4531269247129</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35223,28 +35553,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01269588249513587</v>
+        <v>0.01184126924748838</v>
       </c>
       <c r="J6" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="K6" t="n">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000883184718806107</v>
+        <v>0.0007850976264894838</v>
       </c>
       <c r="M6" t="n">
-        <v>2.394736842289169</v>
+        <v>2.375931317920899</v>
       </c>
       <c r="N6" t="n">
-        <v>10.13985064089734</v>
+        <v>10.04463620154675</v>
       </c>
       <c r="O6" t="n">
-        <v>3.184313213378567</v>
+        <v>3.169327405230762</v>
       </c>
       <c r="P6" t="n">
-        <v>380.1814086461385</v>
+        <v>380.1903756410431</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35301,28 +35631,28 @@
         <v>0.083</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05010179168518973</v>
+        <v>0.05011766107557376</v>
       </c>
       <c r="J7" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="K7" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01351229808192722</v>
+        <v>0.01381185607103785</v>
       </c>
       <c r="M7" t="n">
-        <v>2.44992652246221</v>
+        <v>2.430452054986662</v>
       </c>
       <c r="N7" t="n">
-        <v>10.1767837398529</v>
+        <v>10.08102612385471</v>
       </c>
       <c r="O7" t="n">
-        <v>3.190107167455805</v>
+        <v>3.175063168482592</v>
       </c>
       <c r="P7" t="n">
-        <v>385.4107568118004</v>
+        <v>385.4105795032801</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35379,28 +35709,28 @@
         <v>0.1004</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01148730522424489</v>
+        <v>0.01253898045923212</v>
       </c>
       <c r="J8" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="K8" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0008684951639384986</v>
+        <v>0.001056884916473377</v>
       </c>
       <c r="M8" t="n">
-        <v>2.1625070076633</v>
+        <v>2.146896778015359</v>
       </c>
       <c r="N8" t="n">
-        <v>8.43010810570123</v>
+        <v>8.353200902750686</v>
       </c>
       <c r="O8" t="n">
-        <v>2.903464844922568</v>
+        <v>2.890190461327884</v>
       </c>
       <c r="P8" t="n">
-        <v>382.2838637933912</v>
+        <v>382.2728102355169</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35457,28 +35787,28 @@
         <v>0.1127</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.04249439520926748</v>
+        <v>-0.04309245815024453</v>
       </c>
       <c r="J9" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="K9" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01021186517909844</v>
+        <v>0.01072519256433313</v>
       </c>
       <c r="M9" t="n">
-        <v>2.463876301119614</v>
+        <v>2.444202902119206</v>
       </c>
       <c r="N9" t="n">
-        <v>9.719458053791477</v>
+        <v>9.627860868360267</v>
       </c>
       <c r="O9" t="n">
-        <v>3.117604537748731</v>
+        <v>3.102879447925792</v>
       </c>
       <c r="P9" t="n">
-        <v>379.1734700287957</v>
+        <v>379.1797425149396</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35535,28 +35865,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0975370762008939</v>
+        <v>-0.09676028278019426</v>
       </c>
       <c r="J10" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="K10" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03571997676652394</v>
+        <v>0.0359162351858644</v>
       </c>
       <c r="M10" t="n">
-        <v>3.040143667008292</v>
+        <v>3.014772361769872</v>
       </c>
       <c r="N10" t="n">
-        <v>14.26175729555016</v>
+        <v>14.12646955786592</v>
       </c>
       <c r="O10" t="n">
-        <v>3.776474188386591</v>
+        <v>3.758519596578674</v>
       </c>
       <c r="P10" t="n">
-        <v>381.7828490892736</v>
+        <v>381.774687198422</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35613,28 +35943,28 @@
         <v>0.0667</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2047546272314211</v>
+        <v>-0.2083316497671147</v>
       </c>
       <c r="J11" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="K11" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1467297075007075</v>
+        <v>0.1536220100215128</v>
       </c>
       <c r="M11" t="n">
-        <v>2.902705285508603</v>
+        <v>2.889378740203551</v>
       </c>
       <c r="N11" t="n">
-        <v>13.53871972174677</v>
+        <v>13.4411627996543</v>
       </c>
       <c r="O11" t="n">
-        <v>3.679499928216709</v>
+        <v>3.666219142339189</v>
       </c>
       <c r="P11" t="n">
-        <v>380.4176086017189</v>
+        <v>380.4551733116807</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35691,28 +36021,28 @@
         <v>0.0464</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3034861673000061</v>
+        <v>-0.3089058307110081</v>
       </c>
       <c r="J12" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="K12" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2371877690652261</v>
+        <v>0.2468356061887657</v>
       </c>
       <c r="M12" t="n">
-        <v>3.182980996764109</v>
+        <v>3.179252080053799</v>
       </c>
       <c r="N12" t="n">
-        <v>16.44919819177223</v>
+        <v>16.36626588332086</v>
       </c>
       <c r="O12" t="n">
-        <v>4.05576111128013</v>
+        <v>4.045524179055276</v>
       </c>
       <c r="P12" t="n">
-        <v>384.3927922064578</v>
+        <v>384.4497048399418</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35750,7 +36080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M618"/>
+  <dimension ref="A1:M624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77111,6 +77441,408 @@
         </is>
       </c>
     </row>
+    <row r="619">
+      <c r="A619" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>-36.77020016674051,174.77265543905656</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>-36.76513668630008,174.76780059992754</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>-36.76581801726723,174.76810815502276</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>-36.76643921407013,174.76855292660537</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>-36.7670578692489,174.7689982045381</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>-36.767621749294904,174.76949865669295</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>-36.76815897565904,174.7700505417321</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>-36.768715515203844,174.77061445016133</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>-36.76919330736278,174.7712518123413</t>
+        </is>
+      </c>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>-36.76963556572988,174.77195304837193</t>
+        </is>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>-36.770152924163945,174.7725934184655</t>
+        </is>
+      </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>-36.7702028231368,174.77265064031397</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>-36.765138598973316,174.76779590269473</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>-36.76581887116884,174.76810605580266</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>-36.766442257460646,174.76854593085352</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>-36.76705868658843,174.76899646291926</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>-36.76762408173003,174.76949481022268</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>-36.768160762596246,174.77004817123694</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>-36.76871634059004,174.77061341670353</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>-36.76919662307298,174.77124853625946</t>
+        </is>
+      </c>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>-36.76963802070331,174.77195058672567</t>
+        </is>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>-36.77015515958377,174.77259065244905</t>
+        </is>
+      </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>-36.7702032828977,174.7726498097623</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>-36.765133186514554,174.76780919486353</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>-36.76581557754818,174.76811415279417</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>-36.766438142453666,174.76855538989815</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>-36.7670551447836,174.76900400993387</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>-36.76761816927798,174.76950456057702</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>-36.76815620282535,174.77005422008648</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>-36.768713356501465,174.77061715305086</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>-36.769194153927096,174.77125097589487</t>
+        </is>
+      </c>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>-36.769634653882584,174.77195396269764</t>
+        </is>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>-36.77015356285534,174.7725926281751</t>
+        </is>
+      </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>-36.770205070856626,174.77264657983918</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>-36.765135099188115,174.76780449763118</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>-36.76581655343585,174.76811175368567</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>-36.766439771310665,174.7685516456931</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>-36.76705559886118,174.76900304236793</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>-36.76761871170479,174.7695036660492</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>-36.76815509369184,174.77005569142815</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>-36.768712213659,174.7706185839923</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>-36.769192884080624,174.77125223056447</t>
+        </is>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>-36.76963668800346,174.77195192304794</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>-36.77015381833189,174.77259231205892</t>
+        </is>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>-36.770203078559526,174.77265017889638</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>-36.76513424458931,174.76780659639462</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>-36.765816268801935,174.76811245342566</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>-36.76643947125808,174.76855233541508</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>-36.767056007530975,174.76900217155858</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>-36.767617355637725,174.7695059023688</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>-36.76815429265097,174.77005675406377</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>-36.76871145176402,174.77061953795325</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>-36.76919189642226,174.77125320641855</t>
+        </is>
+      </c>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>-36.76963584629828,174.77195276704094</t>
+        </is>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>-36.77015158291204,174.77259507807526</t>
+        </is>
+      </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>-36.77020251662956,174.77265119401505</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>-36.76512875073898,174.76782008844407</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>-36.76581525225227,174.768114952497</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>-36.76644015709258,174.76855075890768</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>-36.76705650701629,174.76900110723602</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>-36.767616596240146,174.76950715470775</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>-36.76815447750654,174.77005650884016</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>-36.76871037241278,174.7706208893979</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>-36.76919175532821,174.77125334582627</t>
+        </is>
+      </c>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>-36.76963549558778,174.77195311870466</t>
+        </is>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>-36.77015024166008,174.772596737685</t>
+        </is>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0167/nzd0167.xlsx
+++ b/data/nzd0167/nzd0167.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M624"/>
+  <dimension ref="A1:M627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28504,6 +28504,141 @@
         <v>373.87</v>
       </c>
       <c r="M624" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>373.23</v>
+      </c>
+      <c r="C625" t="n">
+        <v>383.84</v>
+      </c>
+      <c r="D625" t="n">
+        <v>374.74</v>
+      </c>
+      <c r="E625" t="n">
+        <v>377.97</v>
+      </c>
+      <c r="F625" t="n">
+        <v>380.01</v>
+      </c>
+      <c r="G625" t="n">
+        <v>387.37</v>
+      </c>
+      <c r="H625" t="n">
+        <v>383.49</v>
+      </c>
+      <c r="I625" t="n">
+        <v>378.62</v>
+      </c>
+      <c r="J625" t="n">
+        <v>379.66</v>
+      </c>
+      <c r="K625" t="n">
+        <v>372.92</v>
+      </c>
+      <c r="L625" t="n">
+        <v>373.16</v>
+      </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>373.19</v>
+      </c>
+      <c r="C626" t="n">
+        <v>385.14</v>
+      </c>
+      <c r="D626" t="n">
+        <v>375.14</v>
+      </c>
+      <c r="E626" t="n">
+        <v>378.56</v>
+      </c>
+      <c r="F626" t="n">
+        <v>379.86</v>
+      </c>
+      <c r="G626" t="n">
+        <v>387.32</v>
+      </c>
+      <c r="H626" t="n">
+        <v>383.44</v>
+      </c>
+      <c r="I626" t="n">
+        <v>378.71</v>
+      </c>
+      <c r="J626" t="n">
+        <v>379.85</v>
+      </c>
+      <c r="K626" t="n">
+        <v>373.26</v>
+      </c>
+      <c r="L626" t="n">
+        <v>373.37</v>
+      </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>372.62</v>
+      </c>
+      <c r="C627" t="n">
+        <v>384.19</v>
+      </c>
+      <c r="D627" t="n">
+        <v>374.45</v>
+      </c>
+      <c r="E627" t="n">
+        <v>377.75</v>
+      </c>
+      <c r="F627" t="n">
+        <v>379.64</v>
+      </c>
+      <c r="G627" t="n">
+        <v>387.01</v>
+      </c>
+      <c r="H627" t="n">
+        <v>383.46</v>
+      </c>
+      <c r="I627" t="n">
+        <v>378.72</v>
+      </c>
+      <c r="J627" t="n">
+        <v>379.51</v>
+      </c>
+      <c r="K627" t="n">
+        <v>373.03</v>
+      </c>
+      <c r="L627" t="n">
+        <v>372.75</v>
+      </c>
+      <c r="M627" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28520,7 +28655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B655"/>
+  <dimension ref="A1:B658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35073,6 +35208,36 @@
       </c>
       <c r="B655" t="n">
         <v>-0.87</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="n">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>-0.9</v>
       </c>
     </row>
   </sheetData>
@@ -35241,28 +35406,28 @@
         <v>0.0446</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3237639875058856</v>
+        <v>-0.3267635794677538</v>
       </c>
       <c r="J2" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="K2" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2897832112087508</v>
+        <v>0.2951479023988701</v>
       </c>
       <c r="M2" t="n">
-        <v>2.956928438873497</v>
+        <v>2.957277383067852</v>
       </c>
       <c r="N2" t="n">
-        <v>14.44076536342874</v>
+        <v>14.41888662522511</v>
       </c>
       <c r="O2" t="n">
-        <v>3.800100704379918</v>
+        <v>3.797220908141257</v>
       </c>
       <c r="P2" t="n">
-        <v>384.8467774507401</v>
+        <v>384.8784147157718</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35319,28 +35484,28 @@
         <v>0.0502</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1377720915732681</v>
+        <v>-0.1376314593478921</v>
       </c>
       <c r="J3" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="K3" t="n">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05785044861265964</v>
+        <v>0.05832092254628796</v>
       </c>
       <c r="M3" t="n">
-        <v>3.232467981444384</v>
+        <v>3.219049795364196</v>
       </c>
       <c r="N3" t="n">
-        <v>17.51973338995992</v>
+        <v>17.43651367945407</v>
       </c>
       <c r="O3" t="n">
-        <v>4.185658059368912</v>
+        <v>4.175705171519425</v>
       </c>
       <c r="P3" t="n">
-        <v>387.9323231984067</v>
+        <v>387.9308446920414</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35397,28 +35562,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1342833581698071</v>
+        <v>-0.1353011224188677</v>
       </c>
       <c r="J4" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="K4" t="n">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1307226862988865</v>
+        <v>0.1335877339615655</v>
       </c>
       <c r="M4" t="n">
-        <v>1.881670527833731</v>
+        <v>1.877813263942854</v>
       </c>
       <c r="N4" t="n">
-        <v>6.776975276693554</v>
+        <v>6.750112890527091</v>
       </c>
       <c r="O4" t="n">
-        <v>2.603262429470674</v>
+        <v>2.598097937054547</v>
       </c>
       <c r="P4" t="n">
-        <v>379.4474950954695</v>
+        <v>379.4582137380589</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35475,28 +35640,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01843976210079783</v>
+        <v>-0.01926119003218254</v>
       </c>
       <c r="J5" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="K5" t="n">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002636652058507272</v>
+        <v>0.002905491547314565</v>
       </c>
       <c r="M5" t="n">
-        <v>1.899438951044583</v>
+        <v>1.894715033846054</v>
       </c>
       <c r="N5" t="n">
-        <v>7.239584984170277</v>
+        <v>7.208916053715328</v>
       </c>
       <c r="O5" t="n">
-        <v>2.690647688600326</v>
+        <v>2.684942467487028</v>
       </c>
       <c r="P5" t="n">
-        <v>379.4531269247129</v>
+        <v>379.4617887395671</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35553,28 +35718,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01184126924748838</v>
+        <v>0.01120414693928377</v>
       </c>
       <c r="J6" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="K6" t="n">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0007850976264894838</v>
+        <v>0.0007103857461217</v>
       </c>
       <c r="M6" t="n">
-        <v>2.375931317920899</v>
+        <v>2.367715503746154</v>
       </c>
       <c r="N6" t="n">
-        <v>10.04463620154675</v>
+        <v>9.998658945897914</v>
       </c>
       <c r="O6" t="n">
-        <v>3.169327405230762</v>
+        <v>3.162065613787594</v>
       </c>
       <c r="P6" t="n">
-        <v>380.1903756410431</v>
+        <v>380.1970936905626</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35631,28 +35796,28 @@
         <v>0.083</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05011766107557376</v>
+        <v>0.05057426751437265</v>
       </c>
       <c r="J7" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="K7" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01381185607103785</v>
+        <v>0.01420950687695766</v>
       </c>
       <c r="M7" t="n">
-        <v>2.430452054986662</v>
+        <v>2.420822347855201</v>
       </c>
       <c r="N7" t="n">
-        <v>10.08102612385471</v>
+        <v>10.03392761797879</v>
       </c>
       <c r="O7" t="n">
-        <v>3.175063168482592</v>
+        <v>3.167637545234427</v>
       </c>
       <c r="P7" t="n">
-        <v>385.4105795032801</v>
+        <v>385.4057654182293</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35709,28 +35874,28 @@
         <v>0.1004</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01253898045923212</v>
+        <v>0.01334776905985332</v>
       </c>
       <c r="J8" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="K8" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001056884916473377</v>
+        <v>0.001209908566695783</v>
       </c>
       <c r="M8" t="n">
-        <v>2.146896778015359</v>
+        <v>2.140347462255217</v>
       </c>
       <c r="N8" t="n">
-        <v>8.353200902750686</v>
+        <v>8.316587926311747</v>
       </c>
       <c r="O8" t="n">
-        <v>2.890190461327884</v>
+        <v>2.883849497860758</v>
       </c>
       <c r="P8" t="n">
-        <v>382.2728102355169</v>
+        <v>382.2642804953739</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35787,28 +35952,28 @@
         <v>0.1127</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.04309245815024453</v>
+        <v>-0.04246556894723467</v>
       </c>
       <c r="J9" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="K9" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01072519256433313</v>
+        <v>0.01052801711813722</v>
       </c>
       <c r="M9" t="n">
-        <v>2.444202902119206</v>
+        <v>2.434972176854963</v>
       </c>
       <c r="N9" t="n">
-        <v>9.627860868360267</v>
+        <v>9.583782637190531</v>
       </c>
       <c r="O9" t="n">
-        <v>3.102879447925792</v>
+        <v>3.095768505103463</v>
       </c>
       <c r="P9" t="n">
-        <v>379.1797425149396</v>
+        <v>379.1731308517332</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35865,28 +36030,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09676028278019426</v>
+        <v>-0.09629211438800039</v>
       </c>
       <c r="J10" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="K10" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0359162351858644</v>
+        <v>0.03595020993074804</v>
       </c>
       <c r="M10" t="n">
-        <v>3.014772361769872</v>
+        <v>3.002562893560476</v>
       </c>
       <c r="N10" t="n">
-        <v>14.12646955786592</v>
+        <v>14.06000974526442</v>
       </c>
       <c r="O10" t="n">
-        <v>3.758519596578674</v>
+        <v>3.749667951334414</v>
       </c>
       <c r="P10" t="n">
-        <v>381.774687198422</v>
+        <v>381.7697507489356</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35943,28 +36108,28 @@
         <v>0.0667</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2083316497671147</v>
+        <v>-0.2100437447217812</v>
       </c>
       <c r="J11" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="K11" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1536220100215128</v>
+        <v>0.1570314388225982</v>
       </c>
       <c r="M11" t="n">
-        <v>2.889378740203551</v>
+        <v>2.88256809667541</v>
       </c>
       <c r="N11" t="n">
-        <v>13.4411627996543</v>
+        <v>13.3921533766376</v>
       </c>
       <c r="O11" t="n">
-        <v>3.666219142339189</v>
+        <v>3.659529119523112</v>
       </c>
       <c r="P11" t="n">
-        <v>380.4551733116807</v>
+        <v>380.4732298311714</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36021,28 +36186,28 @@
         <v>0.0464</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3089058307110081</v>
+        <v>-0.3118291933932131</v>
       </c>
       <c r="J12" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="K12" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2468356061887657</v>
+        <v>0.2518617559472673</v>
       </c>
       <c r="M12" t="n">
-        <v>3.179252080053799</v>
+        <v>3.178344900200268</v>
       </c>
       <c r="N12" t="n">
-        <v>16.36626588332086</v>
+        <v>16.33274996984612</v>
       </c>
       <c r="O12" t="n">
-        <v>4.045524179055276</v>
+        <v>4.041379711168714</v>
       </c>
       <c r="P12" t="n">
-        <v>384.4497048399418</v>
+        <v>384.4805377867774</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36080,7 +36245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M624"/>
+  <dimension ref="A1:M627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77843,6 +78008,207 @@
         </is>
       </c>
     </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>-36.77020629688554,174.77264436503464</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>-36.765127245016785,174.76782378626467</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>-36.765814154378575,174.76811765149398</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>-36.7664385282356,174.76855450311274</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>-36.767056915686084,174.76900023642668</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>-36.76761610805598,174.76950795978277</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>-36.76815447750654,174.77005650884016</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>-36.768707515306495,174.77062446675114</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>-36.769192884080624,174.77125223056447</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>-36.76963717899814,174.77195143071867</t>
+        </is>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>-36.770154776368955,174.7725911266233</t>
+        </is>
+      </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>-36.7702065012237,174.77264399590052</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>-36.76512195464061,174.76783677860624</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>-36.76581252789894,174.76812165000788</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>-36.76643599922057,174.76856031648347</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>-36.76705759680239,174.76899878507768</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>-36.767616379269406,174.76950751251889</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>-36.76815478559921,174.77005610013416</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>-36.76870694388522,174.77062518222178</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>-36.76919154368713,174.77125355493789</t>
+        </is>
+      </c>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>-36.76963479416678,174.77195382203215</t>
+        </is>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>-36.77015343511707,174.77259278623316</t>
+        </is>
+      </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>-36.770209413042224,174.77263873573946</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>-36.76512582068487,174.76782728420298</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>-36.76581533357625,174.76811475257128</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>-36.76643947125808,174.76855233541508</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>-36.76705859577294,174.76899665643248</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>-36.76761806079261,174.7695047394826</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>-36.76815466236214,174.77005626361657</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>-36.76870688039397,174.7706252617185</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>-36.76919394228602,174.7712511850065</t>
+        </is>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>-36.769636407435065,174.77195220437895</t>
+        </is>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>-36.77015739500356,174.77258788643243</t>
+        </is>
+      </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
